--- a/Result/profitability/5701.xlsx
+++ b/Result/profitability/5701.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.11625</v>
+        <v>-0.14625</v>
       </c>
       <c r="N2" t="n">
-        <v>47.06875</v>
+        <v>44.935</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1625</v>
+        <v>-0.1875</v>
       </c>
       <c r="N3" t="n">
-        <v>45.42375</v>
+        <v>43.415</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2025</v>
+        <v>-0.2375</v>
       </c>
       <c r="N4" t="n">
-        <v>43.4525</v>
+        <v>40.87125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.285</v>
+        <v>-0.3</v>
       </c>
       <c r="N5" t="n">
-        <v>41.55625</v>
+        <v>40.15125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.28</v>
+        <v>-0.3</v>
       </c>
       <c r="N6" t="n">
-        <v>40.37375</v>
+        <v>38.82875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,16 +1264,16 @@
         <v>-0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.35</v>
+        <v>-0.4025</v>
       </c>
       <c r="N7" t="n">
-        <v>39.01125</v>
+        <v>36.06625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>-1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5275000000000001</v>
+        <v>-0.5449999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>35.9575</v>
+        <v>34.1525</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>-0.37</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4550000000000001</v>
+        <v>-0.455</v>
       </c>
       <c r="N13" t="n">
         <v>34.1175</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5701</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>100</v>
+      </c>
+      <c r="D75" t="n">
+        <v>67</v>
+      </c>
+      <c r="E75" t="n">
+        <v>33</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-37</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-36.65%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-45</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-45</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.115</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.41375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-14.44</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.304448661184904</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-11.23999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2541261587158037</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
